--- a/data/trans_orig/dukeAFECT-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/dukeAFECT-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la escala de apoyo afectivo (Duke)</t>
+          <t>Puntuación media de la escala de apoyo afectivo (Duke) (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,56; 16,49</t>
+          <t>15,61; 16,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,28; 17,95</t>
+          <t>17,32; 17,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,91; 17,66</t>
+          <t>16,84; 17,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,13; 18,7</t>
+          <t>18,11; 18,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,7; 15,72</t>
+          <t>14,67; 15,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,38; 17,22</t>
+          <t>16,33; 17,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,56; 17,27</t>
+          <t>16,53; 17,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,93; 18,42</t>
+          <t>17,97; 18,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,29; 15,99</t>
+          <t>15,3; 15,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,96; 17,5</t>
+          <t>16,98; 17,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,86; 17,37</t>
+          <t>16,87; 17,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,11; 18,49</t>
+          <t>18,08; 18,48</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,93; 17,52</t>
+          <t>16,92; 17,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,64; 18,17</t>
+          <t>17,65; 18,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,41; 16,88</t>
+          <t>16,41; 16,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,85; 18,32</t>
+          <t>17,83; 18,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,16; 16,83</t>
+          <t>16,15; 16,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,55; 18,06</t>
+          <t>17,56; 18,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,31; 16,75</t>
+          <t>16,3; 16,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,85; 18,24</t>
+          <t>17,82; 18,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,64; 17,07</t>
+          <t>16,62; 17,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,69; 18,05</t>
+          <t>17,69; 18,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,42; 16,73</t>
+          <t>16,43; 16,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,9; 18,21</t>
+          <t>17,91; 18,21</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,05; 18,65</t>
+          <t>18,08; 18,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,04; 18,53</t>
+          <t>18,06; 18,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,07; 17,57</t>
+          <t>17,08; 17,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,86; 18,51</t>
+          <t>17,91; 18,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,19; 18,74</t>
+          <t>18,21; 18,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,56; 18,13</t>
+          <t>17,6; 18,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,85; 17,41</t>
+          <t>16,86; 17,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,75; 18,25</t>
+          <t>17,74; 18,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,23; 18,63</t>
+          <t>18,22; 18,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,86; 18,26</t>
+          <t>17,89; 18,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,05; 17,42</t>
+          <t>17,05; 17,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,91; 18,31</t>
+          <t>17,9; 18,29</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,37; 17,94</t>
+          <t>17,4; 17,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,97; 18,49</t>
+          <t>17,94; 18,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,27; 18,87</t>
+          <t>18,27; 18,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,34; 19,06</t>
+          <t>18,4; 19,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,05; 17,65</t>
+          <t>17,01; 17,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,45; 18,05</t>
+          <t>17,5; 18,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,99; 18,63</t>
+          <t>17,94; 18,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,59; 19,34</t>
+          <t>18,6; 19,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,32; 17,72</t>
+          <t>17,33; 17,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,78; 18,18</t>
+          <t>17,79; 18,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,22; 18,67</t>
+          <t>18,24; 18,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,61; 19,19</t>
+          <t>18,63; 19,13</t>
         </is>
       </c>
     </row>
@@ -1276,37 +1276,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,34; 17,25</t>
+          <t>16,33; 17,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,6; 18,35</t>
+          <t>17,64; 18,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,79; 17,52</t>
+          <t>16,77; 17,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,66; 16,3</t>
+          <t>15,69; 16,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,09; 16,91</t>
+          <t>16,05; 16,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,95; 17,69</t>
+          <t>16,98; 17,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,15; 17,75</t>
+          <t>17,13; 17,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1316,22 +1316,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,31; 16,94</t>
+          <t>16,31; 16,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,38; 17,91</t>
+          <t>17,42; 17,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,07; 17,55</t>
+          <t>17,05; 17,54</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,91; 16,33</t>
+          <t>15,93; 16,34</t>
         </is>
       </c>
     </row>
@@ -1416,47 +1416,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,7; 18,25</t>
+          <t>17,7; 18,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>17,85; 18,4</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>16,8; 17,5</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>17,77; 18,39</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>17,15; 17,9</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>17,5; 18,11</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>16,39; 17,14</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>17,88; 18,4</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>16,86; 17,51</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>17,77; 18,4</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>17,18; 17,9</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>17,48; 18,1</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>16,41; 17,17</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>17,88; 18,41</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,5; 17,98</t>
+          <t>17,52; 17,98</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16,74; 17,27</t>
+          <t>16,73; 17,25</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,93; 18,33</t>
+          <t>17,91; 18,34</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,21; 18,6</t>
+          <t>18,2; 18,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,92; 18,33</t>
+          <t>17,91; 18,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,61; 17,04</t>
+          <t>16,61; 17,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,77; 18,2</t>
+          <t>17,79; 18,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,11; 18,58</t>
+          <t>18,1; 18,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,77; 18,14</t>
+          <t>17,75; 18,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,43; 16,88</t>
+          <t>16,45; 16,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,99; 17,92</t>
+          <t>16,11; 17,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,22; 18,52</t>
+          <t>18,2; 18,51</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,9; 18,17</t>
+          <t>17,93; 18,17</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,6; 16,89</t>
+          <t>16,59; 16,89</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,61; 17,99</t>
+          <t>16,56; 17,97</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,97; 17,37</t>
+          <t>16,95; 17,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,71; 17,07</t>
+          <t>16,71; 17,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,96; 17,3</t>
+          <t>16,98; 17,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,89; 18,75</t>
+          <t>15,88; 18,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,57; 16,96</t>
+          <t>16,55; 16,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,18</t>
+          <t>16,86; 17,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,76; 17,1</t>
+          <t>16,74; 17,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,39; 15,82</t>
+          <t>15,36; 15,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,82; 17,09</t>
+          <t>16,81; 17,09</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,07</t>
+          <t>16,82; 17,07</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16,91; 17,15</t>
+          <t>16,91; 17,16</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,73; 17,73</t>
+          <t>15,73; 17,99</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17,43; 17,65</t>
+          <t>17,44; 17,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1846,32 +1846,32 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,1; 17,28</t>
+          <t>17,1; 17,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17,57; 18,32</t>
+          <t>17,57; 18,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,07; 17,28</t>
+          <t>17,07; 17,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,45; 17,65</t>
+          <t>17,47; 17,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,93; 17,12</t>
+          <t>16,93; 17,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16,97; 17,58</t>
+          <t>16,93; 17,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17,04; 17,18</t>
+          <t>17,04; 17,17</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,36; 17,81</t>
+          <t>17,35; 17,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/dukeAFECT-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/dukeAFECT-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,4</t>
+          <t>18,27</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,22</t>
+          <t>18,21</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,32</t>
+          <t>18,24</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,61; 16,48</t>
+          <t>15,64; 16,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,32; 17,97</t>
+          <t>17,32; 18,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,84; 17,62</t>
+          <t>16,9; 17,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,11; 18,68</t>
+          <t>18,01; 18,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,67; 15,73</t>
+          <t>14,74; 15,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,33; 17,24</t>
+          <t>16,39; 17,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,53; 17,27</t>
+          <t>16,57; 17,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,97; 18,43</t>
+          <t>18,02; 18,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,3; 15,97</t>
+          <t>15,29; 16,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,98; 17,53</t>
+          <t>16,98; 17,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,87; 17,36</t>
+          <t>16,88; 17,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,08; 18,48</t>
+          <t>18,08; 18,4</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18,08</t>
+          <t>18,05</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,27 +823,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>18,03</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>16,86</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>17,89</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>16,58</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>18,04</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>16,86</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>17,89</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>16,58</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>18,06</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,92; 17,55</t>
+          <t>16,94; 17,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,65; 18,19</t>
+          <t>17,68; 18,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,41; 16,86</t>
+          <t>16,4; 16,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,83; 18,31</t>
+          <t>17,8; 18,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,15; 16,83</t>
+          <t>16,17; 16,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,56; 18,06</t>
+          <t>17,58; 18,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,3; 16,76</t>
+          <t>16,28; 16,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,82; 18,23</t>
+          <t>17,83; 18,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,62; 17,1</t>
+          <t>16,64; 17,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,69; 18,08</t>
+          <t>17,71; 18,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,43; 16,74</t>
+          <t>16,42; 16,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,91; 18,21</t>
+          <t>17,88; 18,17</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,23</t>
+          <t>18,18</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,01</t>
+          <t>17,97</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,11</t>
+          <t>18,07</t>
         </is>
       </c>
     </row>
@@ -996,47 +996,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,08; 18,63</t>
+          <t>18,05; 18,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,06; 18,55</t>
+          <t>18,01; 18,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,08; 17,57</t>
+          <t>17,08; 17,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,91; 18,54</t>
+          <t>17,84; 18,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,21; 18,75</t>
+          <t>18,21; 18,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,6; 18,13</t>
+          <t>17,55; 18,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,86; 17,41</t>
+          <t>16,82; 17,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,74; 18,25</t>
+          <t>17,69; 18,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,22; 18,62</t>
+          <t>18,24; 18,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,05; 17,41</t>
+          <t>17,04; 17,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,9; 18,29</t>
+          <t>17,87; 18,25</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,76</t>
+          <t>18,67</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,91</t>
+          <t>18,61</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,85</t>
+          <t>18,63</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,4; 17,96</t>
+          <t>17,41; 17,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,94; 18,49</t>
+          <t>17,96; 18,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,27; 18,84</t>
+          <t>18,28; 18,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,4; 19,06</t>
+          <t>18,22; 19,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,01; 17,64</t>
+          <t>17,0; 17,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,5; 18,05</t>
+          <t>17,45; 18,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,94; 18,64</t>
+          <t>17,99; 18,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,6; 19,34</t>
+          <t>18,34; 18,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,33; 17,73</t>
+          <t>17,3; 17,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,79; 18,19</t>
+          <t>17,78; 18,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,24; 18,67</t>
+          <t>18,23; 18,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,63; 19,13</t>
+          <t>18,37; 18,83</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,0</t>
+          <t>15,98</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,23</t>
+          <t>16,19</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,13</t>
+          <t>16,09</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,33; 17,26</t>
+          <t>16,28; 17,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,64; 18,36</t>
+          <t>17,69; 18,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,77; 17,49</t>
+          <t>16,78; 17,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,69; 16,32</t>
+          <t>15,64; 16,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,05; 16,86</t>
+          <t>16,0; 16,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,98; 17,71</t>
+          <t>16,96; 17,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,13; 17,75</t>
+          <t>17,15; 17,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,99; 16,45</t>
+          <t>15,96; 16,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,31; 16,96</t>
+          <t>16,32; 16,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,42; 17,94</t>
+          <t>17,42; 17,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,05; 17,54</t>
+          <t>17,07; 17,54</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,93; 16,34</t>
+          <t>15,88; 16,28</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18,12</t>
+          <t>17,99</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18,15</t>
+          <t>18,09</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,14</t>
+          <t>18,04</t>
         </is>
       </c>
     </row>
@@ -1416,42 +1416,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,7; 18,22</t>
+          <t>17,69; 18,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,85; 18,4</t>
+          <t>17,83; 18,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,8; 17,5</t>
+          <t>16,87; 17,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,77; 18,39</t>
+          <t>17,61; 18,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,15; 17,9</t>
+          <t>17,14; 17,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,5; 18,11</t>
+          <t>17,47; 18,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,39; 17,14</t>
+          <t>16,41; 17,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,88; 18,4</t>
+          <t>17,79; 18,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17,75; 18,17</t>
+          <t>17,75; 18,16</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16,73; 17,25</t>
+          <t>16,75; 17,25</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,91; 18,34</t>
+          <t>17,8; 18,24</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18,0</t>
+          <t>17,92</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>17,16</t>
+          <t>17,77</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,52</t>
+          <t>17,84</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,2; 18,58</t>
+          <t>18,19; 18,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,91; 18,32</t>
+          <t>17,91; 18,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,61; 17,05</t>
+          <t>16,62; 17,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,79; 18,22</t>
+          <t>17,7; 18,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,1; 18,56</t>
+          <t>18,08; 18,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,75; 18,15</t>
+          <t>17,78; 18,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,45; 16,89</t>
+          <t>16,47; 16,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,11; 17,92</t>
+          <t>17,55; 17,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,2; 18,51</t>
+          <t>18,22; 18,51</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,93; 18,17</t>
+          <t>17,89; 18,18</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,59; 16,89</t>
+          <t>16,59; 16,9</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,56; 17,97</t>
+          <t>17,69; 17,99</t>
         </is>
       </c>
     </row>
@@ -1643,47 +1643,47 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>15,94</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>16,75</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>17,01</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>16,94</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>15,56</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>16,96</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>16,96</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
           <t>17,03</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>16,75</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>17,01</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>16,94</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>15,59</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>16,96</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>16,96</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>17,03</t>
-        </is>
-      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>15,74</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,95; 17,36</t>
+          <t>16,96; 17,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1706,22 +1706,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,98; 17,32</t>
+          <t>16,97; 17,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,88; 18,63</t>
+          <t>15,66; 16,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,55; 16,93</t>
+          <t>16,55; 16,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,86; 17,19</t>
+          <t>16,84; 17,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1731,17 +1731,17 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,36; 15,79</t>
+          <t>15,33; 15,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,81; 17,09</t>
+          <t>16,8; 17,09</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16,82; 17,07</t>
+          <t>16,82; 17,08</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,73; 17,99</t>
+          <t>15,59; 15,93</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17,78</t>
+          <t>17,51</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>17,38</t>
+          <t>17,39</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>17,58</t>
+          <t>17,45</t>
         </is>
       </c>
     </row>
@@ -1836,47 +1836,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17,44; 17,64</t>
+          <t>17,45; 17,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,71; 17,89</t>
+          <t>17,72; 17,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,1; 17,29</t>
+          <t>17,11; 17,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17,57; 18,25</t>
+          <t>17,41; 17,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,07; 17,29</t>
+          <t>17,06; 17,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,47; 17,65</t>
+          <t>17,46; 17,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,93; 17,11</t>
+          <t>16,93; 17,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16,93; 17,58</t>
+          <t>17,3; 17,48</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17,28; 17,43</t>
+          <t>17,28; 17,44</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,35; 17,82</t>
+          <t>17,38; 17,52</t>
         </is>
       </c>
     </row>
